--- a/public/templates/office/EMP_DEG_120_인터페이스설계서.xlsx
+++ b/public/templates/office/EMP_DEG_120_인터페이스설계서.xlsx
@@ -3286,7 +3286,7 @@
       </c>
       <c r="C12" s="163" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 SyncGuard AI 시스템 구축</t>
+          <t>한빛글로벌 SyncGuard AI 시스템 구축</t>
         </is>
       </c>
       <c r="D12" s="164" t="n"/>
@@ -3341,13 +3341,13 @@
     <row r="22" ht="22.5" customHeight="1" s="276">
       <c r="C22" s="171" t="inlineStr">
         <is>
-          <t>그로브소프트 (EMPASY)</t>
+          <t>엠파시 (EMPASY)</t>
         </is>
       </c>
       <c r="D22" s="172" t="n"/>
       <c r="E22" s="169" t="inlineStr">
         <is>
-          <t>아모레퍼시픽</t>
+          <t>한빛글로벌</t>
         </is>
       </c>
       <c r="F22" s="170" t="n"/>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="F4" s="78" t="inlineStr">
         <is>
-          <t>아모레퍼시픽</t>
+          <t>한빛글로벌</t>
         </is>
       </c>
     </row>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="D5" s="81" t="inlineStr">
         <is>
-          <t>대외 연계 API 서버(server-api :18085) 전담화, 티움넷 의뢰 수신 및 확정 결과(HTML/JSON) 회신, 300MB 대용량 파일 직접 업로드, ProductLab 매일 02:00 일배치, 실증자료 요청 이메일 연동 반영</t>
+          <t>대외 연계 API 서버(server-api :18085) 전담화, 마케팅허브 의뢰 수신 및 확정 결과(HTML/JSON) 회신, 300MB 대용량 파일 직접 업로드, ProductLab 매일 02:00 일배치, 실증자료 요청 이메일 연동 반영</t>
         </is>
       </c>
       <c r="E5" s="82" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="D6" s="81" t="inlineStr">
         <is>
-          <t>BO ALB(사용자대역 오픈) / 대외연계 ALB(티움넷 서버만 오픈) 물리 분리, 대외연계·BO 서버 ➔ AI Agent EKS Service 호출, S3 Intelligent-Tiering 자동 적용, 네이버 클로바 OCR 및 상용 LLM Outbound URL/서버 접속정보 추가</t>
+          <t>BO ALB(사용자대역 오픈) / 대외연계 ALB(마케팅허브 서버만 오픈) 물리 분리, 대외연계·BO 서버 ➔ AI Agent EKS Service 호출, S3 Intelligent-Tiering 자동 적용, 네이버 클로바 OCR 및 상용 LLM Outbound URL/서버 접속정보 추가</t>
         </is>
       </c>
       <c r="E6" s="82" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="C5" s="62" t="inlineStr">
         <is>
-          <t>티움넷 심의 의뢰 및 시안 접수</t>
+          <t>마케팅허브 심의 의뢰 및 시안 접수</t>
         </is>
       </c>
       <c r="D5" s="63" t="inlineStr">
         <is>
-          <t>티움넷 서버만 오픈된 대외 연계 전용 ALB(syncguard-api.hanbitglobal.com)를 통해 광고 심의 의뢰 메타데이터 수신 (300MB 시안·동영상은 대외 연계 API 서버 S3 Presigned URL 및 Intelligent-Tiering으로 직접 업로드)</t>
+          <t>마케팅허브 서버만 오픈된 대외 연계 전용 ALB(syncguard-api.hanbitglobal.com)를 통해 광고 심의 의뢰 메타데이터 수신 (300MB 시안·동영상은 대외 연계 API 서버 S3 Presigned URL 및 Intelligent-Tiering으로 직접 업로드)</t>
         </is>
       </c>
       <c r="E5" s="65" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="L5" s="64" t="inlineStr">
         <is>
-          <t>티움넷운영팀</t>
+          <t>마케팅허브운영팀</t>
         </is>
       </c>
       <c r="M5" s="64" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="P5" s="64" t="inlineStr">
         <is>
-          <t>장지용 PL</t>
+          <t>최현우 PL</t>
         </is>
       </c>
       <c r="Q5" s="64" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="T5" s="53" t="inlineStr">
         <is>
-          <t>장지용 PL</t>
+          <t>최현우 PL</t>
         </is>
       </c>
       <c r="U5" s="66" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>티움넷 대조뷰어 링크 및 최종결과 회신</t>
+          <t>마케팅허브 대조뷰어 링크 및 최종결과 회신</t>
         </is>
       </c>
       <c r="D6" s="39" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="L6" s="33" t="inlineStr">
         <is>
-          <t>장지용 PL</t>
+          <t>최현우 PL</t>
         </is>
       </c>
       <c r="M6" s="33" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="P6" s="33" t="inlineStr">
         <is>
-          <t>티움넷운영팀</t>
+          <t>마케팅허브운영팀</t>
         </is>
       </c>
       <c r="Q6" s="33" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="T6" s="35" t="inlineStr">
         <is>
-          <t>장지용 PL</t>
+          <t>최현우 PL</t>
         </is>
       </c>
       <c r="U6" s="38" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="L7" s="33" t="inlineStr">
         <is>
-          <t>장지용 PL</t>
+          <t>최현우 PL</t>
         </is>
       </c>
       <c r="M7" s="33" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="T7" s="280" t="inlineStr">
         <is>
-          <t>장지용 PL</t>
+          <t>최현우 PL</t>
         </is>
       </c>
       <c r="U7" s="38" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="P8" s="33" t="inlineStr">
         <is>
-          <t>장지용 PL</t>
+          <t>최현우 PL</t>
         </is>
       </c>
       <c r="Q8" s="33" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="T8" s="280" t="inlineStr">
         <is>
-          <t>장지용 PL</t>
+          <t>최현우 PL</t>
         </is>
       </c>
       <c r="U8" s="36" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="L9" s="33" t="inlineStr">
         <is>
-          <t>장지용 PL</t>
+          <t>최현우 PL</t>
         </is>
       </c>
       <c r="M9" s="33" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="T9" s="280" t="inlineStr">
         <is>
-          <t>장지용 PL</t>
+          <t>최현우 PL</t>
         </is>
       </c>
       <c r="U9" s="38" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="L10" s="33" t="inlineStr">
         <is>
-          <t>장지용 PL</t>
+          <t>최현우 PL</t>
         </is>
       </c>
       <c r="M10" s="33" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="T10" s="280" t="inlineStr">
         <is>
-          <t>장지용 PL</t>
+          <t>최현우 PL</t>
         </is>
       </c>
       <c r="U10" s="38" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="L11" s="33" t="inlineStr">
         <is>
-          <t>오병문 AA</t>
+          <t>박준혁 AA</t>
         </is>
       </c>
       <c r="M11" s="33" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="T11" s="43" t="inlineStr">
         <is>
-          <t>오병문 AA</t>
+          <t>박준혁 AA</t>
         </is>
       </c>
       <c r="U11" s="38" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="L12" s="33" t="inlineStr">
         <is>
-          <t>장지용 PL</t>
+          <t>최현우 PL</t>
         </is>
       </c>
       <c r="M12" s="33" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="T12" s="43" t="inlineStr">
         <is>
-          <t>장지용 PL</t>
+          <t>최현우 PL</t>
         </is>
       </c>
       <c r="U12" s="38" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="L13" s="33" t="inlineStr">
         <is>
-          <t>장지용 PL</t>
+          <t>최현우 PL</t>
         </is>
       </c>
       <c r="M13" s="33" t="inlineStr">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="T13" s="43" t="inlineStr">
         <is>
-          <t>장지용 PL</t>
+          <t>최현우 PL</t>
         </is>
       </c>
       <c r="U13" s="38" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="L14" s="33" t="inlineStr">
         <is>
-          <t>장지용 PL</t>
+          <t>최현우 PL</t>
         </is>
       </c>
       <c r="M14" s="33" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="P14" s="33" t="inlineStr">
         <is>
-          <t>장지용 PL</t>
+          <t>최현우 PL</t>
         </is>
       </c>
       <c r="Q14" s="33" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="T14" s="43" t="inlineStr">
         <is>
-          <t>장지용 PL</t>
+          <t>최현우 PL</t>
         </is>
       </c>
       <c r="U14" s="38" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="G14" s="213" t="inlineStr">
         <is>
-          <t>티움넷 서버만 오픈</t>
+          <t>마케팅허브 서버만 오픈</t>
         </is>
       </c>
       <c r="H14" s="108" t="inlineStr">
@@ -7569,7 +7569,7 @@
       </c>
       <c r="J14" s="108" t="inlineStr">
         <is>
-          <t>연계 ALB (티움넷 전용)</t>
+          <t>연계 ALB (마케팅허브 전용)</t>
         </is>
       </c>
       <c r="K14" s="108" t="n"/>
@@ -9332,14 +9332,14 @@
     <row r="3" ht="18.75" customFormat="1" customHeight="1" s="229">
       <c r="A3" s="95" t="inlineStr">
         <is>
-          <t>그로브소프트 연계개발팀 / 아모레퍼시픽 IT</t>
+          <t>엠파시 연계개발팀 / 한빛글로벌 IT</t>
         </is>
       </c>
       <c r="B3" s="228" t="n"/>
       <c r="N3" s="230" t="n"/>
       <c r="O3" s="216" t="inlineStr">
         <is>
-          <t>그로브소프트 연계개발팀</t>
+          <t>엠파시 연계개발팀</t>
         </is>
       </c>
       <c r="P3" s="217" t="n"/>
@@ -10831,14 +10831,14 @@
       </c>
       <c r="F7" s="253" t="inlineStr">
         <is>
-          <t>인터페이스명: 티움넷·마이비커·SSO·[Option]KT레몬 연계</t>
+          <t>인터페이스명: 마케팅허브·프로덕트랩·SSO·[Option]KT레몬 연계</t>
         </is>
       </c>
       <c r="G7" s="198" t="n"/>
       <c r="H7" s="199" t="n"/>
       <c r="I7" s="261" t="inlineStr">
         <is>
-          <t>티움넷 의뢰/결과 연동, 마이비커 전성분·실증 조회, [Option] KT 레몬 벡터 검색</t>
+          <t>마케팅허브 의뢰/결과 연동, 프로덕트랩 전성분·실증 조회, [Option] KT 레몬 벡터 검색</t>
         </is>
       </c>
       <c r="J7" s="178" t="n"/>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="I11" s="274" t="inlineStr">
         <is>
-          <t>티움넷 시안·동영상 심의 의뢰 수신</t>
+          <t>마케팅허브 시안·동영상 심의 의뢰 수신</t>
         </is>
       </c>
       <c r="J11" s="274" t="inlineStr">

--- a/public/templates/office/EMP_DEG_120_인터페이스설계서.xlsx
+++ b/public/templates/office/EMP_DEG_120_인터페이스설계서.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문서이력" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="인터페이스목록" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="접속정보" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="매핑정보_IF-EXT-02_MarketingHub" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="매핑정보_IF-EXT-02_SRM-Portal" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="인터페이스 설계서-상세" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
@@ -65,7 +65,7 @@
     <definedName name="MM개발자" localSheetId="3">#REF!</definedName>
     <definedName name="MM난위도" localSheetId="3">#REF!</definedName>
     <definedName name="MM테스트여부" localSheetId="3">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'매핑정보_IF-EXT-02_MarketingHub'!$B$2:$S$48</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'매핑정보_IF-EXT-02_SRM-Portal'!$B$2:$S$48</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'인터페이스 설계서-상세'!$A$1:$N$28</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="C12" s="163" t="inlineStr">
         <is>
-          <t>한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
       <c r="D12" s="164" t="n"/>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="D4" s="76" t="inlineStr">
         <is>
-          <t>SyncGuard AI 시스템 구축 기준 상세 작성</t>
+          <t>SyncFlow AI 시스템 구축 기준 상세 작성</t>
         </is>
       </c>
       <c r="E4" s="77" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="D5" s="81" t="inlineStr">
         <is>
-          <t>대외 연계 API 서버(server-api :18085) 전담화, 마케팅허브 의뢰 수신 및 확정 결과(HTML/JSON) 회신, 300MB 대용량 파일 직접 업로드, ProductLab 매일 02:00 일배치, 실증자료 요청 이메일 연동 반영</t>
+          <t>대외 연계 API 서버(server-api :18085) 전담화, 전자구매포털 의뢰 수신 및 확정 결과(HTML/JSON) 회신, 300MB 대용량 파일 직접 업로드, PLM-Nexus 매일 02:00 일배치, 시험성적서 요청 이메일 연동 반영</t>
         </is>
       </c>
       <c r="E5" s="82" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="D6" s="81" t="inlineStr">
         <is>
-          <t>BO ALB(사용자대역 오픈) / 대외연계 ALB(마케팅허브 서버만 오픈) 물리 분리, 대외연계·BO 서버 ➔ AI Agent EKS Service 호출, S3 Intelligent-Tiering 자동 적용, 네이버 클로바 OCR 및 상용 LLM Outbound URL/서버 접속정보 추가</t>
+          <t>BO ALB(사용자대역 오픈) / 대외연계 ALB(전자구매포털 서버만 오픈) 물리 분리, 대외연계·BO 서버 ➔ AI Agent EKS Service 호출, S3 Intelligent-Tiering 자동 적용, 엔터프라이즈 비전 OCR 및 상용 LLM Outbound URL/서버 접속정보 추가</t>
         </is>
       </c>
       <c r="E6" s="82" t="inlineStr">
@@ -3854,17 +3854,17 @@
       </c>
       <c r="B5" s="61" t="inlineStr">
         <is>
-          <t>IF-MKTH-001</t>
+          <t>IF-SRM-001</t>
         </is>
       </c>
       <c r="C5" s="62" t="inlineStr">
         <is>
-          <t>마케팅허브 심의 의뢰 및 시안 접수</t>
+          <t>전자구매포털 검증 요청 및 계약·도서 접수</t>
         </is>
       </c>
       <c r="D5" s="63" t="inlineStr">
         <is>
-          <t>마케팅허브 서버만 오픈된 대외 연계 전용 ALB(syncguard-api.hanbitglobal.com)를 통해 광고 심의 의뢰 메타데이터 수신 (300MB 시안·동영상은 대외 연계 API 서버 S3 Presigned URL 및 Intelligent-Tiering으로 직접 업로드)</t>
+          <t>전자구매포털 서버만 오픈된 대외 연계 전용 ALB(syncflow-api.hanbitglobal.com)를 통해 계약·규격 검증 의뢰 메타데이터 수신 (300MB 계약·도서·설계도면은 대외 연계 API 서버 S3 Presigned URL 및 Intelligent-Tiering으로 직접 업로드)</t>
         </is>
       </c>
       <c r="E5" s="65" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="K5" s="64" t="inlineStr">
         <is>
-          <t>MarketingHub</t>
+          <t>SRM-Portal</t>
         </is>
       </c>
       <c r="L5" s="64" t="inlineStr">
         <is>
-          <t>마케팅허브운영팀</t>
+          <t>전자구매포털운영팀</t>
         </is>
       </c>
       <c r="M5" s="64" t="inlineStr">
@@ -3914,12 +3914,12 @@
       </c>
       <c r="N5" s="64" t="inlineStr">
         <is>
-          <t>POST /api/v1/if/marketinghub/request</t>
+          <t>POST /api/v1/if/srm-portal/request</t>
         </is>
       </c>
       <c r="O5" s="64" t="inlineStr">
         <is>
-          <t>SyncGuard AI</t>
+          <t>SyncFlow AI</t>
         </is>
       </c>
       <c r="P5" s="64" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="R5" s="64" t="inlineStr">
         <is>
-          <t>review_request</t>
+          <t>verify_request</t>
         </is>
       </c>
       <c r="S5" s="278" t="inlineStr">
@@ -3959,17 +3959,17 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>IF-MKTH-002</t>
+          <t>IF-SRM-002</t>
         </is>
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>마케팅허브 대조뷰어 링크 및 최종결과 회신</t>
+          <t>전자구매포털 대조뷰어 링크 및 최종결과 회신</t>
         </is>
       </c>
       <c r="D6" s="39" t="inlineStr">
         <is>
-          <t>AI 1차 판정 뷰어 링크 및 RA 최종 승인/반려 결과·PDF 회신</t>
+          <t>AI 1차 판정 뷰어 링크 및 QA 최종 승인/반려 결과·PDF 회신</t>
         </is>
       </c>
       <c r="E6" s="34" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="K6" s="33" t="inlineStr">
         <is>
-          <t>SyncGuard AI</t>
+          <t>SyncFlow AI</t>
         </is>
       </c>
       <c r="L6" s="33" t="inlineStr">
@@ -4019,17 +4019,17 @@
       </c>
       <c r="N6" s="33" t="inlineStr">
         <is>
-          <t>IF_REVIEW_RESULT_OUT</t>
+          <t>IF_VERIFY_RESULT_OUT</t>
         </is>
       </c>
       <c r="O6" s="33" t="inlineStr">
         <is>
-          <t>MarketingHub</t>
+          <t>SRM-Portal</t>
         </is>
       </c>
       <c r="P6" s="33" t="inlineStr">
         <is>
-          <t>마케팅허브운영팀</t>
+          <t>전자구매포털운영팀</t>
         </is>
       </c>
       <c r="Q6" s="33" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="R6" s="33" t="inlineStr">
         <is>
-          <t>POST /api/claim/callback</t>
+          <t>POST /api/Spec/callback</t>
         </is>
       </c>
       <c r="S6" s="35" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="C7" s="30" t="inlineStr">
         <is>
-          <t>ProductLab 전성분·원료 배합규격 조회</t>
+          <t>PLM-Nexus 자재BOM·원소재 조성규격 조회</t>
         </is>
       </c>
       <c r="D7" s="30" t="inlineStr">
         <is>
-          <t>제품/처방코드 기준 전성분 목록 및 식약처 배합한도 실시간 조회</t>
+          <t>제품/설계사양코드 기준 자재BOM 목록 및 공정위·표준원 유해물질한도 실시간 조회</t>
         </is>
       </c>
       <c r="E7" s="40" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="K7" s="33" t="inlineStr">
         <is>
-          <t>SyncGuard AI</t>
+          <t>SyncFlow AI</t>
         </is>
       </c>
       <c r="L7" s="33" t="inlineStr">
@@ -4129,12 +4129,12 @@
       </c>
       <c r="O7" s="33" t="inlineStr">
         <is>
-          <t>ProductLab</t>
+          <t>PLM-Nexus</t>
         </is>
       </c>
       <c r="P7" s="33" t="inlineStr">
         <is>
-          <t>R&amp;I연구소</t>
+          <t>선행연구소연구소</t>
         </is>
       </c>
       <c r="Q7" s="33" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="U7" s="38" t="inlineStr">
         <is>
-          <t>전성분대조</t>
+          <t>자재BOM대조</t>
         </is>
       </c>
     </row>
@@ -4174,12 +4174,12 @@
       </c>
       <c r="C8" s="30" t="inlineStr">
         <is>
-          <t>ProductLab 인체적용시험 실증보고서 연동</t>
+          <t>PLM-Nexus 공인신뢰성시험 시험검증보고서 연동</t>
         </is>
       </c>
       <c r="D8" s="30" t="inlineStr">
         <is>
-          <t>효능·수치 소구 문장 검증용 인체적용시험·세포효능 성적서 조회</t>
+          <t>성능규격·수치 기술사양 조항 검증용 공인신뢰성시험·배상한도성능규격 성적서 조회</t>
         </is>
       </c>
       <c r="E8" s="40" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="K8" s="33" t="inlineStr">
         <is>
-          <t>ProductLab</t>
+          <t>PLM-Nexus</t>
         </is>
       </c>
       <c r="L8" s="33" t="inlineStr">
         <is>
-          <t>R&amp;I연구소</t>
+          <t>선행연구소연구소</t>
         </is>
       </c>
       <c r="M8" s="33" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="O8" s="33" t="inlineStr">
         <is>
-          <t>SyncGuard AI</t>
+          <t>SyncFlow AI</t>
         </is>
       </c>
       <c r="P8" s="33" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="R8" s="33" t="inlineStr">
         <is>
-          <t>review_evidence</t>
+          <t>verify_evidence</t>
         </is>
       </c>
       <c r="S8" s="280" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="U8" s="36" t="inlineStr">
         <is>
-          <t>실증근거</t>
+          <t>시험검증근거</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="D9" s="41" t="inlineStr">
         <is>
-          <t>마케터(FO)/RA·관리자(BO) HB-SSO SSO 로그인 및 IAM 기반 BO 관리자 권한 검증(validateBoAdminPermission)</t>
+          <t>구매담당자(FO)/QA·관리자(BO) HB-SSO SSO 로그인 및 IAM 기반 BO 관리자 권한 검증(validateBoAdminPermission)</t>
         </is>
       </c>
       <c r="E9" s="40" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="K9" s="33" t="inlineStr">
         <is>
-          <t>SyncGuard AI</t>
+          <t>SyncFlow AI</t>
         </is>
       </c>
       <c r="L9" s="33" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="C10" s="30" t="inlineStr">
         <is>
-          <t>AWS S3 시안 원본 및 동영상 스냅샷 저장</t>
+          <t>AWS S3 계약·도서 원본 및 설계도면 스냅샷 저장</t>
         </is>
       </c>
       <c r="D10" s="42" t="inlineStr">
         <is>
-          <t>대용량 시안·동영상(300MB), AI 1차 추출 피크프레임 및 웹 사용자 보정 캡처 장면 S3 업로드 (Storage Class: Intelligent-Tiering 자동 적용으로 보관비용 최적화)</t>
+          <t>대용량 계약·도서·설계도면(300MB), AI 1차 추출 도면스냅샷 및 웹 사용자 보정 도면 스냅샷 S3 업로드 (Storage Class: Intelligent-Tiering 자동 적용으로 보관비용 최적화)</t>
         </is>
       </c>
       <c r="E10" s="40" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="K10" s="33" t="inlineStr">
         <is>
-          <t>SyncGuard AI</t>
+          <t>SyncFlow AI</t>
         </is>
       </c>
       <c r="L10" s="33" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="R10" s="33" t="inlineStr">
         <is>
-          <t>s3://ap-syncguard-ai-prd</t>
+          <t>s3://ap-syncflow-ai-prd</t>
         </is>
       </c>
       <c r="S10" s="280" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="C11" s="30" t="inlineStr">
         <is>
-          <t>[Option] KT 레몬 연구보고서 벡터 검색</t>
+          <t>[Option] HB-Monitor 연구보고서 벡터 검색</t>
         </is>
       </c>
       <c r="D11" s="32" t="inlineStr">
         <is>
-          <t>[선택사양] R&amp;I 연구보고서 벡터 유사도 검색 (상용 LLM 파싱과 비교 후 결정)</t>
+          <t>[선택사양] 선행연구소 연구보고서 벡터 유사도 검색 (상용 LLM 파싱과 비교 후 결정)</t>
         </is>
       </c>
       <c r="E11" s="40" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="K11" s="33" t="inlineStr">
         <is>
-          <t>SyncGuard AI</t>
+          <t>SyncFlow AI</t>
         </is>
       </c>
       <c r="L11" s="33" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="O11" s="33" t="inlineStr">
         <is>
-          <t>KT 레몬</t>
+          <t>HB-Monitor</t>
         </is>
       </c>
       <c r="P11" s="33" t="inlineStr">
         <is>
-          <t>R&amp;I연구소</t>
+          <t>선행연구소연구소</t>
         </is>
       </c>
       <c r="Q11" s="33" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="C12" s="30" t="inlineStr">
         <is>
-          <t>네이버 클로바 OCR API 연동</t>
+          <t>엔터프라이즈 비전 OCR API 연동</t>
         </is>
       </c>
       <c r="D12" s="32" t="inlineStr">
         <is>
-          <t>이미지 시안, AI 추출 피크프레임 및 웹 사용자 보정 캡처 장면 한글/영문 OCR 텍스트·좌표 추출 (Outbound 방화벽 오픈)</t>
+          <t>이미지 계약·도서, AI 추출 도면스냅샷 및 웹 사용자 보정 도면 스냅샷 한글/영문 OCR 텍스트·좌표 추출 (Outbound 방화벽 오픈)</t>
         </is>
       </c>
       <c r="E12" s="40" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="K12" s="33" t="inlineStr">
         <is>
-          <t>SyncGuard AI (Agent :18083)</t>
+          <t>SyncFlow AI (Agent :18083)</t>
         </is>
       </c>
       <c r="L12" s="33" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="N12" s="33" t="inlineStr">
         <is>
-          <t>NaverClovaOcrClient</t>
+          <t>EnterpriseVisionOcrClient</t>
         </is>
       </c>
       <c r="O12" s="33" t="inlineStr">
         <is>
-          <t>네이버 클라우드 (CLOVA OCR)</t>
+          <t>사내 표준 (Enterprise Vision OCR)</t>
         </is>
       </c>
       <c r="P12" s="33" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="R12" s="33" t="inlineStr">
         <is>
-          <t>https://*.apigw.ntruss.com</t>
+          <t>https://ocr-api.hanbitglobal.internal</t>
         </is>
       </c>
       <c r="S12" s="43" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="D13" s="32" t="inlineStr">
         <is>
-          <t>비학습(Zero Data Retention) 상용 LLM 3단계 심의 판정 및 1536차원 벡터 임베딩 호출 (Outbound 방화벽 오픈)</t>
+          <t>비학습(Zero Data Retention) 상용 LLM 3단계 검증 판정 및 1536차원 벡터 임베딩 호출 (Outbound 방화벽 오픈)</t>
         </is>
       </c>
       <c r="E13" s="40" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="K13" s="33" t="inlineStr">
         <is>
-          <t>SyncGuard AI (Agent :18083)</t>
+          <t>SyncFlow AI (Agent :18083)</t>
         </is>
       </c>
       <c r="L13" s="33" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="D14" s="32" t="inlineStr">
         <is>
-          <t>대외연계 서버(1차 피크프레임 추출·심의) 및 BO 업무서버(웹 동영상 재생·특정화면 멈춤 장면 추가/편집/삭제 보정·수동 재실행)에서 EKS Service로 AI Agent 호출</t>
+          <t>대외연계 서버(1차 도면 규격영역 추출·검증) 및 BO 업무서버(웹 설계도면 재생·특정화면 멈춤 장면 추가/편집/삭제 보정·수동 재실행)에서 EKS Service로 AI Agent 호출</t>
         </is>
       </c>
       <c r="E14" s="40" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="N14" s="33" t="inlineStr">
         <is>
-          <t>SyncGuardAgentClient</t>
+          <t>SyncFlowAgentClient</t>
         </is>
       </c>
       <c r="O14" s="33" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="R14" s="33" t="inlineStr">
         <is>
-          <t>http://syncguard-ai-agent-svc:18083</t>
+          <t>http://syncflow-ai-agent-svc:18083</t>
         </is>
       </c>
       <c r="S14" s="43" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="G5" s="213" t="inlineStr">
         <is>
-          <t>review_svc_acc</t>
+          <t>verify_svc_acc</t>
         </is>
       </c>
       <c r="H5" s="136" t="inlineStr">
@@ -7072,7 +7072,7 @@
     <row r="6" ht="18.75" customHeight="1" s="276">
       <c r="A6" s="213" t="inlineStr">
         <is>
-          <t>MarketingHub 심의시스템</t>
+          <t>SRM-Portal 검증시스템</t>
         </is>
       </c>
       <c r="B6" s="213" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="C6" s="213" t="inlineStr">
         <is>
-          <t>mkthub-api.hanbitglobal.com</t>
+          <t>srm-api.hanbitglobal.com</t>
         </is>
       </c>
       <c r="D6" s="150" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="E6" s="213" t="inlineStr">
         <is>
-          <t>MKTHUBDB</t>
+          <t>SRMDB</t>
         </is>
       </c>
       <c r="F6" s="150" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="G6" s="213" t="inlineStr">
         <is>
-          <t>mkthub_review_user</t>
+          <t>srmp_verify_user</t>
         </is>
       </c>
       <c r="H6" s="108" t="inlineStr">
         <is>
-          <t>https://mkthub-api.hanbitglobal.com</t>
+          <t>https://srm-api.hanbitglobal.com</t>
         </is>
       </c>
       <c r="I6" s="108" t="inlineStr">
@@ -7130,7 +7130,7 @@
     <row r="7" ht="18.75" customHeight="1" s="276">
       <c r="A7" s="213" t="inlineStr">
         <is>
-          <t>[Option] KT 레몬 (연구보고서 RAG)</t>
+          <t>[Option] HB-Monitor (연구보고서 RAG)</t>
         </is>
       </c>
       <c r="B7" s="213" t="inlineStr">
@@ -7188,7 +7188,7 @@
     <row r="8" ht="18.75" customHeight="1" s="276">
       <c r="A8" s="213" t="inlineStr">
         <is>
-          <t>ProductLab (전성분·실증DB)</t>
+          <t>PLM-Nexus (자재BOM·시험검증DB)</t>
         </is>
       </c>
       <c r="B8" s="213" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C8" s="213" t="inlineStr">
         <is>
-          <t>productlab-core.hanbitglobal.com</t>
+          <t>plmnexus-core.hanbitglobal.com</t>
         </is>
       </c>
       <c r="D8" s="150" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="E8" s="213" t="inlineStr">
         <is>
-          <t>PRODLABDB</t>
+          <t>PLMNEXUSDB</t>
         </is>
       </c>
       <c r="F8" s="150" t="inlineStr">
@@ -7218,12 +7218,12 @@
       </c>
       <c r="G8" s="213" t="inlineStr">
         <is>
-          <t>prodlab_read_user</t>
+          <t>plmnexus_read_user</t>
         </is>
       </c>
       <c r="H8" s="108" t="inlineStr">
         <is>
-          <t>https://productlab-core.hanbitglobal.com</t>
+          <t>https://plmnexus-core.hanbitglobal.com</t>
         </is>
       </c>
       <c r="I8" s="108" t="inlineStr">
@@ -7246,7 +7246,7 @@
     <row r="9" ht="18.75" customHeight="1" s="276">
       <c r="A9" s="213" t="inlineStr">
         <is>
-          <t>SyncGuard AI 운영DB</t>
+          <t>SyncFlow AI 운영DB</t>
         </is>
       </c>
       <c r="B9" s="213" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="C9" s="213" t="inlineStr">
         <is>
-          <t>syncguard-db.hanbitglobal.com</t>
+          <t>syncflow-db.hanbitglobal.com</t>
         </is>
       </c>
       <c r="D9" s="150" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="E9" s="213" t="inlineStr">
         <is>
-          <t>syncguard_db</t>
+          <t>syncflow_db</t>
         </is>
       </c>
       <c r="F9" s="150" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="G9" s="213" t="inlineStr">
         <is>
-          <t>review_app_user</t>
+          <t>verify_app_user</t>
         </is>
       </c>
       <c r="H9" s="108" t="n"/>
@@ -7292,17 +7292,17 @@
     <row r="10" ht="18.75" customHeight="1" s="276">
       <c r="A10" s="213" t="inlineStr">
         <is>
-          <t>네이버 클로바 OCR (Outbound)</t>
+          <t>엔터프라이즈 비전 OCR (Outbound)</t>
         </is>
       </c>
       <c r="B10" s="213" t="inlineStr">
         <is>
-          <t>CLOVA OCR API</t>
+          <t>Enterprise Vision OCR API</t>
         </is>
       </c>
       <c r="C10" s="213" t="inlineStr">
         <is>
-          <t>*.apigw.ntruss.com</t>
+          <t>ocr-api.hanbitglobal.internal</t>
         </is>
       </c>
       <c r="D10" s="150" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="H10" s="108" t="inlineStr">
         <is>
-          <t>https://*.apigw.ntruss.com</t>
+          <t>https://ocr-api.hanbitglobal.internal</t>
         </is>
       </c>
       <c r="I10" s="108" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="E12" s="213" t="inlineStr">
         <is>
-          <t>ap-syncguard-ai-prd/stg/dev</t>
+          <t>ap-syncflow-ai-prd/stg/dev</t>
         </is>
       </c>
       <c r="F12" s="150" t="inlineStr">
@@ -7466,7 +7466,7 @@
     <row r="13" ht="18.75" customHeight="1" s="276">
       <c r="A13" s="213" t="inlineStr">
         <is>
-          <t>SyncGuard AI BO 전용 ALB (Inbound)</t>
+          <t>SyncFlow AI BO 전용 ALB (Inbound)</t>
         </is>
       </c>
       <c r="B13" s="213" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="C13" s="213" t="inlineStr">
         <is>
-          <t>claim.hanbitglobal.com</t>
+          <t>Spec.hanbitglobal.com</t>
         </is>
       </c>
       <c r="D13" s="150" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="H13" s="108" t="inlineStr">
         <is>
-          <t>https://claim.hanbitglobal.com</t>
+          <t>https://Spec.hanbitglobal.com</t>
         </is>
       </c>
       <c r="I13" s="108" t="inlineStr">
@@ -7524,7 +7524,7 @@
     <row r="14" ht="18.75" customHeight="1" s="276">
       <c r="A14" s="213" t="inlineStr">
         <is>
-          <t>SyncGuard AI 대외연계 전용 ALB (Inbound)</t>
+          <t>SyncFlow AI 대외연계 전용 ALB (Inbound)</t>
         </is>
       </c>
       <c r="B14" s="213" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="C14" s="213" t="inlineStr">
         <is>
-          <t>syncguard-api.hanbitglobal.com</t>
+          <t>syncflow-api.hanbitglobal.com</t>
         </is>
       </c>
       <c r="D14" s="150" t="inlineStr">
@@ -7554,12 +7554,12 @@
       </c>
       <c r="G14" s="213" t="inlineStr">
         <is>
-          <t>마케팅허브 서버만 오픈</t>
+          <t>전자구매포털 서버만 오픈</t>
         </is>
       </c>
       <c r="H14" s="108" t="inlineStr">
         <is>
-          <t>https://syncguard-api.hanbitglobal.com</t>
+          <t>https://syncflow-api.hanbitglobal.com</t>
         </is>
       </c>
       <c r="I14" s="108" t="inlineStr">
@@ -7569,7 +7569,7 @@
       </c>
       <c r="J14" s="108" t="inlineStr">
         <is>
-          <t>연계 ALB (마케팅허브 전용)</t>
+          <t>연계 ALB (전자구매포털 전용)</t>
         </is>
       </c>
       <c r="K14" s="108" t="n"/>
@@ -7582,7 +7582,7 @@
     <row r="15" ht="18.75" customHeight="1" s="276">
       <c r="A15" s="213" t="inlineStr">
         <is>
-          <t>SyncGuard AI Agent 내부 서비스 (Internal)</t>
+          <t>SyncFlow AI Agent 내부 서비스 (Internal)</t>
         </is>
       </c>
       <c r="B15" s="213" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="C15" s="213" t="inlineStr">
         <is>
-          <t>syncguard-ai-agent-svc</t>
+          <t>syncflow-ai-agent-svc</t>
         </is>
       </c>
       <c r="D15" s="150" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="H15" s="108" t="inlineStr">
         <is>
-          <t>http://syncguard-ai-agent-svc:18083</t>
+          <t>http://syncflow-ai-agent-svc:18083</t>
         </is>
       </c>
       <c r="I15" s="108" t="inlineStr">
@@ -7640,7 +7640,7 @@
     <row r="16" ht="18.75" customHeight="1" s="276">
       <c r="A16" s="213" t="inlineStr">
         <is>
-          <t>실증요청 메일 서버 (Outbound)</t>
+          <t>성적서요청 메일 서버 (Outbound)</t>
         </is>
       </c>
       <c r="B16" s="213" t="inlineStr">
@@ -9372,7 +9372,7 @@
     <row r="6" ht="25.5" customFormat="1" customHeight="1" s="229">
       <c r="B6" s="197" t="inlineStr">
         <is>
-          <t>Source : SyncGuard AI (송신)</t>
+          <t>Source : SyncFlow AI (송신)</t>
         </is>
       </c>
       <c r="C6" s="198" t="n"/>
@@ -9383,7 +9383,7 @@
       <c r="H6" s="199" t="n"/>
       <c r="I6" s="234" t="inlineStr">
         <is>
-          <t>Target : MarketingHub 광고심의시스템 (수신)</t>
+          <t>Target : SRM-Portal 계약·규격검증시스템 (수신)</t>
         </is>
       </c>
       <c r="J6" s="178" t="n"/>
@@ -9415,7 +9415,7 @@
       <c r="C7" s="196" t="n"/>
       <c r="D7" s="213" t="inlineStr">
         <is>
-          <t>IF_REVIEW_RESULT_OUT</t>
+          <t>IF_VERIFY_RESULT_OUT</t>
         </is>
       </c>
       <c r="E7" s="198" t="n"/>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C9" s="213" t="inlineStr">
         <is>
-          <t>review_request</t>
+          <t>verify_request</t>
         </is>
       </c>
       <c r="D9" s="151" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="H9" s="213" t="inlineStr">
         <is>
-          <t>심의신청번호</t>
+          <t>검증신청번호</t>
         </is>
       </c>
       <c r="I9" s="213" t="inlineStr">
         <is>
-          <t>MKTHUB_REQ_NO</t>
+          <t>SRM_REQ_NO</t>
         </is>
       </c>
       <c r="J9" s="150" t="inlineStr">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="C10" s="213" t="inlineStr">
         <is>
-          <t>review_request</t>
+          <t>verify_request</t>
         </is>
       </c>
       <c r="D10" s="154" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="H10" s="213" t="inlineStr">
         <is>
-          <t>브랜드코드</t>
+          <t>사업본부코드</t>
         </is>
       </c>
       <c r="I10" s="213" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="C11" s="213" t="inlineStr">
         <is>
-          <t>review_request</t>
+          <t>verify_request</t>
         </is>
       </c>
       <c r="D11" s="154" t="inlineStr">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="C12" s="213" t="inlineStr">
         <is>
-          <t>review_request</t>
+          <t>verify_request</t>
         </is>
       </c>
       <c r="D12" s="154" t="inlineStr">
@@ -9783,7 +9783,7 @@
       </c>
       <c r="C13" s="213" t="inlineStr">
         <is>
-          <t>review_request</t>
+          <t>verify_request</t>
         </is>
       </c>
       <c r="D13" s="154" t="inlineStr">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="C14" s="213" t="inlineStr">
         <is>
-          <t>review_request</t>
+          <t>verify_request</t>
         </is>
       </c>
       <c r="D14" s="154" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="H14" s="154" t="inlineStr">
         <is>
-          <t>심의결과PDF다운로드URL</t>
+          <t>검증결과PDF다운로드URL</t>
         </is>
       </c>
       <c r="I14" s="213" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="C15" s="213" t="inlineStr">
         <is>
-          <t>review_request</t>
+          <t>verify_request</t>
         </is>
       </c>
       <c r="D15" s="154" t="inlineStr">
@@ -9932,12 +9932,12 @@
       </c>
       <c r="H15" s="154" t="inlineStr">
         <is>
-          <t>RA전문가최종검토의견</t>
+          <t>법무·QA전문위원최종검토의견</t>
         </is>
       </c>
       <c r="I15" s="213" t="inlineStr">
         <is>
-          <t>RA_COMMENT</t>
+          <t>QA_COMMENT</t>
         </is>
       </c>
       <c r="J15" s="150" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="C16" s="213" t="inlineStr">
         <is>
-          <t>review_request</t>
+          <t>verify_request</t>
         </is>
       </c>
       <c r="D16" s="154" t="inlineStr">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="H16" s="154" t="inlineStr">
         <is>
-          <t>심의확정일시</t>
+          <t>검증확정일시</t>
         </is>
       </c>
       <c r="I16" s="213" t="inlineStr">
@@ -10559,7 +10559,7 @@
     <row r="43" ht="21" customHeight="1" s="276" thickBot="1">
       <c r="B43" s="203" t="inlineStr">
         <is>
-          <t>심의 확정 일시 포맷 변환 (TIMESTAMP -&gt; YYYYMMDDHH24MISS)</t>
+          <t>검증 확정 일시 포맷 변환 (TIMESTAMP -&gt; YYYYMMDDHH24MISS)</t>
         </is>
       </c>
       <c r="C43" s="204" t="n"/>
@@ -10603,7 +10603,7 @@
     <row r="45" ht="69.75" customHeight="1" s="276">
       <c r="B45" s="238" t="inlineStr">
         <is>
-          <t>RA 전문가가 심의 콘솔에서 최종 판정(승인/조건부승인/반려) 확정 버튼 클릭 시 즉시 트리거</t>
+          <t>법무·QA 전문위원가 검증 콘솔에서 최종 판정(승인/조건부승인/반려) 확정 버튼 클릭 시 즉시 트리거</t>
         </is>
       </c>
       <c r="C45" s="239" t="n"/>
@@ -10627,7 +10627,7 @@
     <row r="46" ht="69.75" customHeight="1" s="276">
       <c r="B46" s="193" t="inlineStr">
         <is>
-          <t>review_request.status IN ('APPROVED', 'CONDITIONAL', 'REJECTED') AND mkthub_sync_yn = 'N'</t>
+          <t>verify_request.status IN ('APPROVED', 'CONDITIONAL', 'REJECTED') AND srm_sync_yn = 'N'</t>
         </is>
       </c>
       <c r="C46" s="194" t="n"/>
@@ -10651,7 +10651,7 @@
     <row r="47" ht="69.75" customHeight="1" s="276">
       <c r="B47" s="193" t="inlineStr">
         <is>
-          <t>HTTPS POST(JSON + HMAC-SHA256 서명) 호출 후 HTTP 200 ACK 수신 시 mkthub_sync_yn = 'Y' 갱신</t>
+          <t>HTTPS POST(JSON + HMAC-SHA256 서명) 호출 후 HTTP 200 ACK 수신 시 srm_sync_yn = 'Y' 갱신</t>
         </is>
       </c>
       <c r="C47" s="194" t="n"/>
@@ -10814,7 +10814,7 @@
     <row r="7" ht="19.5" customHeight="1" s="276">
       <c r="A7" s="253" t="inlineStr">
         <is>
-          <t>시스템명: SyncGuard AI</t>
+          <t>시스템명: SyncFlow AI</t>
         </is>
       </c>
       <c r="B7" s="199" t="n"/>
@@ -10826,26 +10826,26 @@
       <c r="D7" s="179" t="n"/>
       <c r="E7" s="253" t="inlineStr">
         <is>
-          <t>인터페이스ID: IF-MKTH-001 ~ IF-LEM-001</t>
+          <t>인터페이스ID: IF-SRM-001 ~ IF-LEM-001</t>
         </is>
       </c>
       <c r="F7" s="253" t="inlineStr">
         <is>
-          <t>인터페이스명: 마케팅허브·프로덕트랩·SSO·[Option]KT레몬 연계</t>
+          <t>인터페이스명: 전자구매포털·피엘엠넥서스·SSO·[Option]HB-Monitor 연계</t>
         </is>
       </c>
       <c r="G7" s="198" t="n"/>
       <c r="H7" s="199" t="n"/>
       <c r="I7" s="261" t="inlineStr">
         <is>
-          <t>마케팅허브 의뢰/결과 연동, 프로덕트랩 전성분·실증 조회, [Option] KT 레몬 벡터 검색</t>
+          <t>전자구매포털 의뢰/결과 연동, 피엘엠넥서스 자재BOM·시험검증 조회, [Option] HB-Monitor 벡터 검색</t>
         </is>
       </c>
       <c r="J7" s="178" t="n"/>
       <c r="K7" s="179" t="n"/>
       <c r="L7" s="261" t="inlineStr">
         <is>
-          <t>심의의뢰/결과, 전성분/실증, 인증토큰</t>
+          <t>검증요청/결과, 자재BOM/시험검증, 인증토큰</t>
         </is>
       </c>
       <c r="M7" s="178" t="n"/>
@@ -10981,12 +10981,12 @@
       </c>
       <c r="B11" s="158" t="inlineStr">
         <is>
-          <t>MarketingHub</t>
+          <t>SRM-Portal</t>
         </is>
       </c>
       <c r="C11" s="158" t="inlineStr">
         <is>
-          <t>MarketingHubWebhookController</t>
+          <t>SrmPortalWebhookController</t>
         </is>
       </c>
       <c r="D11" s="157" t="inlineStr">
@@ -11001,7 +11001,7 @@
       </c>
       <c r="F11" s="157" t="inlineStr">
         <is>
-          <t>심의 신청 시</t>
+          <t>검증 신청 시</t>
         </is>
       </c>
       <c r="G11" s="157" t="inlineStr">
@@ -11011,17 +11011,17 @@
       </c>
       <c r="H11" s="274" t="inlineStr">
         <is>
-          <t>ReviewIntakeService</t>
+          <t>ContractIntakeService</t>
         </is>
       </c>
       <c r="I11" s="274" t="inlineStr">
         <is>
-          <t>마케팅허브 시안·동영상 심의 의뢰 수신</t>
+          <t>전자구매포털 계약·도서·설계도면 검증 요청 수신</t>
         </is>
       </c>
       <c r="J11" s="274" t="inlineStr">
         <is>
-          <t>IF-MKTH-001</t>
+          <t>IF-SRM-001</t>
         </is>
       </c>
       <c r="K11" s="274" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="B12" s="160" t="inlineStr">
         <is>
-          <t>SyncGuard AI</t>
+          <t>SyncFlow AI</t>
         </is>
       </c>
       <c r="C12" s="160" t="inlineStr">
         <is>
-          <t>MarketingHubCallbackService</t>
+          <t>SrmPortalCallbackService</t>
         </is>
       </c>
       <c r="D12" s="159" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="F12" s="159" t="inlineStr">
         <is>
-          <t>RA 확정 시</t>
+          <t>QA 확정 시</t>
         </is>
       </c>
       <c r="G12" s="159" t="inlineStr">
@@ -11072,17 +11072,17 @@
       </c>
       <c r="H12" s="0" t="inlineStr">
         <is>
-          <t>MarketingHubResultReceiver</t>
+          <t>SrmPortalResultReceiver</t>
         </is>
       </c>
       <c r="I12" s="0" t="inlineStr">
         <is>
-          <t>AI 대조뷰어 링크 및 RA 최종 결과 회신</t>
+          <t>AI 대조뷰어 링크 및 QA 최종 결과 회신</t>
         </is>
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t>IF-MKTH-002</t>
+          <t>IF-SRM-002</t>
         </is>
       </c>
       <c r="K12" s="0" t="inlineStr">
@@ -11100,12 +11100,12 @@
       </c>
       <c r="B13" s="160" t="inlineStr">
         <is>
-          <t>SyncGuard AI</t>
+          <t>SyncFlow AI</t>
         </is>
       </c>
       <c r="C13" s="160" t="inlineStr">
         <is>
-          <t>ProductLabFormulaClient</t>
+          <t>PlmNexusSpecClient</t>
         </is>
       </c>
       <c r="D13" s="159" t="inlineStr">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="F13" s="159" t="inlineStr">
         <is>
-          <t>심의 시 / 일 1회</t>
+          <t>검증 시 / 일 1회</t>
         </is>
       </c>
       <c r="G13" s="159" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="H13" s="0" t="inlineStr">
         <is>
-          <t>ProductLabApiProvider</t>
+          <t>PlmNexusApiProvider</t>
         </is>
       </c>
       <c r="I13" s="0" t="inlineStr">
         <is>
-          <t>제품 전성분·배합한도 및 인체적용시험 실증 연동</t>
+          <t>제품 자재BOM·유해물질한도 및 공인신뢰성시험 시험검증 연동</t>
         </is>
       </c>
       <c r="J13" s="0" t="inlineStr">
